--- a/artfynd/A 49753-2022 artfynd.xlsx
+++ b/artfynd/A 49753-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49753-2022 artfynd.xlsx
+++ b/artfynd/A 49753-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105923595</v>
+        <v>105923594</v>
       </c>
       <c r="B2" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>813028.608749127</v>
+        <v>813066</v>
       </c>
       <c r="R2" t="n">
-        <v>7316599.807081655</v>
+        <v>7316552</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>2022-09-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105923593</v>
+        <v>105923596</v>
       </c>
       <c r="B3" t="n">
-        <v>78595</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>813126.1959427544</v>
+        <v>812992</v>
       </c>
       <c r="R3" t="n">
-        <v>7316551.024877665</v>
+        <v>7316643</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -860,19 +840,9 @@
           <t>2022-09-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105923594</v>
+        <v>105923598</v>
       </c>
       <c r="B4" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>813066.085303653</v>
+        <v>812962</v>
       </c>
       <c r="R4" t="n">
-        <v>7316552.277515257</v>
+        <v>7316566</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -972,19 +937,9 @@
           <t>2022-09-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105923600</v>
+        <v>105923593</v>
       </c>
       <c r="B5" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>813007.9453396073</v>
+        <v>813126</v>
       </c>
       <c r="R5" t="n">
-        <v>7316324.447388179</v>
+        <v>7316551</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1084,19 +1034,9 @@
           <t>2022-09-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105923596</v>
+        <v>105923595</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>812991.9899307478</v>
+        <v>813028</v>
       </c>
       <c r="R6" t="n">
-        <v>7316643.298928809</v>
+        <v>7316599</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1196,19 +1131,9 @@
           <t>2022-09-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105923598</v>
+        <v>105923600</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>812962.044205352</v>
+        <v>813008</v>
       </c>
       <c r="R7" t="n">
-        <v>7316565.65035489</v>
+        <v>7316324</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1308,19 +1228,9 @@
           <t>2022-09-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105923597</v>
+        <v>112365064</v>
       </c>
       <c r="B8" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,16 +1268,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1387,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>812950.858893337</v>
+        <v>813211</v>
       </c>
       <c r="R8" t="n">
-        <v>7316584.666819943</v>
+        <v>7316203</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,22 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,12 +1342,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1462,12 +1357,7 @@
         <v>105923590</v>
       </c>
       <c r="B9" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>813287.6550349913</v>
+        <v>813288</v>
       </c>
       <c r="R9" t="n">
-        <v>7316267.139773012</v>
+        <v>7316267</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1532,19 +1422,9 @@
           <t>2022-09-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,54 +1451,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111906849</v>
+        <v>105923597</v>
       </c>
       <c r="B10" t="n">
-        <v>89879</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ej möjlig att validera</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6039940</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mandarinfingersvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria tridentina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schild</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Torrkölen (Torrkölen), Nb</t>
+          <t>Flarken, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>813178</v>
+        <v>812951</v>
       </c>
       <c r="R10" t="n">
-        <v>7316200</v>
+        <v>7316585</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1642,22 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,117 +1536,15 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>112365064</v>
-      </c>
-      <c r="B11" t="n">
-        <v>95815</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>221941</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Plattlummer</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Lycopodium complanatum</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Flarken, Nb</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>813211</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7316203</v>
-      </c>
-      <c r="S11" t="n">
-        <v>25</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Överluleå</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Linnea Åsedahl</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Linnea Åsedahl</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49753-2022 artfynd.xlsx
+++ b/artfynd/A 49753-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105923594</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105923596</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105923598</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105923593</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105923595</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105923600</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112365064</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105923597</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,8 +1590,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105923590</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>